--- a/tool/chem.xlsx
+++ b/tool/chem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pp/Desktop/CS_SWU_68/CP242/organic-chem-app/tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CC83F1-815C-D84B-A680-5313764277D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C98705-EA46-9247-88EA-41AB49B98300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="13" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>molecularFormula</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Chemical</t>
+  </si>
+  <si>
+    <t>functiongroup</t>
   </si>
 </sst>
 </file>
@@ -257,24 +260,18 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9DAF8"/>
-        <bgColor rgb="FFC9DAF8"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -289,19 +286,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,32 +507,34 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="3">
+      <c r="D2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -554,9 +543,12 @@
       <c r="C3" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="3">
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -565,9 +557,12 @@
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="3">
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -576,9 +571,12 @@
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="3">
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -587,9 +585,12 @@
       <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="3">
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -598,9 +599,12 @@
       <c r="C7" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="3">
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -609,9 +613,12 @@
       <c r="C8" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="3">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -620,9 +627,12 @@
       <c r="C9" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="3">
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -631,9 +641,12 @@
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="3">
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -642,9 +655,12 @@
       <c r="C11" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="3">
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -653,9 +669,12 @@
       <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="3">
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -664,9 +683,12 @@
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="3">
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -675,9 +697,12 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2">
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -686,9 +711,12 @@
       <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="2">
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -697,9 +725,12 @@
       <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="2">
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -708,9 +739,12 @@
       <c r="C17" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="2">
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -719,9 +753,12 @@
       <c r="C18" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="2">
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -730,9 +767,12 @@
       <c r="C19" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="2">
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -741,9 +781,12 @@
       <c r="C20" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="2">
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -752,9 +795,12 @@
       <c r="C21" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="2">
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -763,9 +809,12 @@
       <c r="C22" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="2">
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -774,9 +823,12 @@
       <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="2">
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -785,9 +837,12 @@
       <c r="C24" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="2">
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -796,9 +851,12 @@
       <c r="C25" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="3">
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -807,9 +865,12 @@
       <c r="C26" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="3">
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -818,9 +879,12 @@
       <c r="C27" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="3">
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -829,9 +893,12 @@
       <c r="C28" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="3">
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -840,9 +907,12 @@
       <c r="C29" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="3">
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -851,9 +921,12 @@
       <c r="C30" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="3">
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -862,9 +935,12 @@
       <c r="C31" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="3">
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -873,9 +949,12 @@
       <c r="C32" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="3">
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -884,9 +963,12 @@
       <c r="C33" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="3">
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -895,9 +977,12 @@
       <c r="C34" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="3">
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -906,9 +991,12 @@
       <c r="C35" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="3">
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -917,9 +1005,12 @@
       <c r="C36" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="2">
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -928,11 +1019,11 @@
       <c r="C37" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="D37" s="1">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/tool/chem.xlsx
+++ b/tool/chem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pp/Desktop/CS_SWU_68/CP242/organic-chem-app/tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C98705-EA46-9247-88EA-41AB49B98300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDF7CCC-526F-8E43-AC36-B496BBE313B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="78">
   <si>
     <t>molecularFormula</t>
   </si>
@@ -238,13 +238,22 @@
     <t>Dodecyne</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>Chemical</t>
-  </si>
-  <si>
     <t>functiongroup</t>
+  </si>
+  <si>
+    <t>chemical</t>
+  </si>
+  <si>
+    <t>Alkane</t>
+  </si>
+  <si>
+    <t>Alkene</t>
+  </si>
+  <si>
+    <t>Alkyne</t>
+  </si>
+  <si>
+    <t>Aromatic</t>
   </si>
 </sst>
 </file>
@@ -521,507 +530,435 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1">
-        <v>1</v>
+      <c r="A3" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1">
+      <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
+      <c r="B27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="1">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="1">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="1">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="1">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="1">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="1">
-        <v>27</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="1">
-        <v>28</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="1">
-        <v>29</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="1">
+      <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="1">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="1">
-        <v>32</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="1">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="1">
-        <v>34</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="1">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="1">
-        <v>4</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D37" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tool/chem.xlsx
+++ b/tool/chem.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pp/Desktop/CS_SWU_68/CP242/organic-chem-app/tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4732D24E-9C93-5141-895C-59D7027B9CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78C34E8-84F2-9E46-A07B-D497BE64F786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chemical" sheetId="13" r:id="rId1"/>
     <sheet name="Reaction" sheetId="14" r:id="rId2"/>
     <sheet name="Condition" sheetId="15" r:id="rId3"/>
-    <sheet name="User" sheetId="16" r:id="rId4"/>
+    <sheet name="User" sheetId="18" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="717">
   <si>
     <t>molecularFormula</t>
   </si>
@@ -292,24 +292,6 @@
     <t>Δ</t>
   </si>
   <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>admin1</t>
-  </si>
-  <si>
     <t>Chemical</t>
   </si>
   <si>
@@ -2156,6 +2138,42 @@
   </si>
   <si>
     <t>KOH</t>
+  </si>
+  <si>
+    <t>Substitution reaction</t>
+  </si>
+  <si>
+    <t>การฟอกจางสีสารละลาย เกิดปฏิกิริยาแทนที่</t>
+  </si>
+  <si>
+    <t>Addition reaction</t>
+  </si>
+  <si>
+    <t>การฟอกจางสีสารละลาย เกิดปฏิกิริยาการเติม</t>
+  </si>
+  <si>
+    <t>Esterification</t>
+  </si>
+  <si>
+    <t>ปฏิกิริยาเอสเทอริฟิเคชัน</t>
+  </si>
+  <si>
+    <t>Hydrolysis ester</t>
+  </si>
+  <si>
+    <t>ปฏิกิริยาไฮโดรไลซิสเอสเทอร์</t>
+  </si>
+  <si>
+    <t>Synthesis amide </t>
+  </si>
+  <si>
+    <t>ปฏิกิรยาการสังเคราะห์เอไมด์ </t>
+  </si>
+  <si>
+    <t>Hydrolysis amide </t>
+  </si>
+  <si>
+    <t>ปฏิกิรยาไฮโดรไลซิสของเอไมด์</t>
   </si>
 </sst>
 </file>
@@ -2441,7 +2459,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1"/>
@@ -2911,10 +2929,10 @@
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>73</v>
@@ -2945,10 +2963,10 @@
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>73</v>
@@ -2979,10 +2997,10 @@
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>73</v>
@@ -3013,10 +3031,10 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>73</v>
@@ -3047,10 +3065,10 @@
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>73</v>
@@ -3081,10 +3099,10 @@
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>73</v>
@@ -3115,10 +3133,10 @@
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>73</v>
@@ -3149,10 +3167,10 @@
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>73</v>
@@ -3183,10 +3201,10 @@
     </row>
     <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>73</v>
@@ -3217,10 +3235,10 @@
     </row>
     <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>73</v>
@@ -3251,10 +3269,10 @@
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>73</v>
@@ -3285,10 +3303,10 @@
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>73</v>
@@ -3319,10 +3337,10 @@
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>73</v>
@@ -3353,10 +3371,10 @@
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>73</v>
@@ -3387,10 +3405,10 @@
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>73</v>
@@ -3421,10 +3439,10 @@
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>73</v>
@@ -3455,10 +3473,10 @@
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>73</v>
@@ -3489,10 +3507,10 @@
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>73</v>
@@ -3523,10 +3541,10 @@
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>73</v>
@@ -3557,10 +3575,10 @@
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>73</v>
@@ -3591,10 +3609,10 @@
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>73</v>
@@ -3625,10 +3643,10 @@
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>73</v>
@@ -3659,10 +3677,10 @@
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>73</v>
@@ -3693,10 +3711,10 @@
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>73</v>
@@ -3727,10 +3745,10 @@
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>73</v>
@@ -3761,10 +3779,10 @@
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>73</v>
@@ -3795,10 +3813,10 @@
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>73</v>
@@ -3829,10 +3847,10 @@
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>73</v>
@@ -3863,10 +3881,10 @@
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>73</v>
@@ -3897,10 +3915,10 @@
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>73</v>
@@ -3931,10 +3949,10 @@
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>73</v>
@@ -3965,10 +3983,10 @@
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>73</v>
@@ -3999,10 +4017,10 @@
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>73</v>
@@ -4033,10 +4051,10 @@
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>73</v>
@@ -4067,10 +4085,10 @@
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>74</v>
@@ -4101,10 +4119,10 @@
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>74</v>
@@ -4135,10 +4153,10 @@
     </row>
     <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>74</v>
@@ -4169,10 +4187,10 @@
     </row>
     <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>74</v>
@@ -4203,10 +4221,10 @@
     </row>
     <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>74</v>
@@ -4237,10 +4255,10 @@
     </row>
     <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>74</v>
@@ -4271,10 +4289,10 @@
     </row>
     <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>74</v>
@@ -4305,10 +4323,10 @@
     </row>
     <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>74</v>
@@ -4339,10 +4357,10 @@
     </row>
     <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>74</v>
@@ -4373,10 +4391,10 @@
     </row>
     <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>74</v>
@@ -4407,10 +4425,10 @@
     </row>
     <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>74</v>
@@ -5223,10 +5241,10 @@
     </row>
     <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>76</v>
@@ -5257,13 +5275,13 @@
     </row>
     <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -5291,13 +5309,13 @@
     </row>
     <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -5325,13 +5343,13 @@
     </row>
     <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -5359,13 +5377,13 @@
     </row>
     <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -5393,13 +5411,13 @@
     </row>
     <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -5427,13 +5445,13 @@
     </row>
     <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -5461,13 +5479,13 @@
     </row>
     <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -5495,13 +5513,13 @@
     </row>
     <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -5529,13 +5547,13 @@
     </row>
     <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
@@ -5563,13 +5581,13 @@
     </row>
     <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -5597,13 +5615,13 @@
     </row>
     <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -5631,13 +5649,13 @@
     </row>
     <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
@@ -5665,13 +5683,13 @@
     </row>
     <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
@@ -5699,13 +5717,13 @@
     </row>
     <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
@@ -5733,13 +5751,13 @@
     </row>
     <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
@@ -5767,13 +5785,13 @@
     </row>
     <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
@@ -5801,13 +5819,13 @@
     </row>
     <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
@@ -5835,13 +5853,13 @@
     </row>
     <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
@@ -5869,13 +5887,13 @@
     </row>
     <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
@@ -5903,13 +5921,13 @@
     </row>
     <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -5937,13 +5955,13 @@
     </row>
     <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
@@ -5971,13 +5989,13 @@
     </row>
     <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
@@ -6005,13 +6023,13 @@
     </row>
     <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -6039,13 +6057,13 @@
     </row>
     <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -6073,13 +6091,13 @@
     </row>
     <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
@@ -6107,13 +6125,13 @@
     </row>
     <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -6141,13 +6159,13 @@
     </row>
     <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -6175,13 +6193,13 @@
     </row>
     <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
@@ -6209,13 +6227,13 @@
     </row>
     <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
@@ -6243,13 +6261,13 @@
     </row>
     <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
@@ -6277,13 +6295,13 @@
     </row>
     <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
@@ -6311,13 +6329,13 @@
     </row>
     <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
@@ -6345,13 +6363,13 @@
     </row>
     <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -6379,13 +6397,13 @@
     </row>
     <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -6413,13 +6431,13 @@
     </row>
     <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -6447,13 +6465,13 @@
     </row>
     <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -6481,13 +6499,13 @@
     </row>
     <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -6515,13 +6533,13 @@
     </row>
     <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -6549,13 +6567,13 @@
     </row>
     <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -6583,13 +6601,13 @@
     </row>
     <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -6617,13 +6635,13 @@
     </row>
     <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -6651,13 +6669,13 @@
     </row>
     <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -6685,13 +6703,13 @@
     </row>
     <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -6719,13 +6737,13 @@
     </row>
     <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -6753,13 +6771,13 @@
     </row>
     <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -6787,13 +6805,13 @@
     </row>
     <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -6821,13 +6839,13 @@
     </row>
     <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -6855,13 +6873,13 @@
     </row>
     <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -6889,13 +6907,13 @@
     </row>
     <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B132" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -6923,13 +6941,13 @@
     </row>
     <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -6957,13 +6975,13 @@
     </row>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -6991,13 +7009,13 @@
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -7025,13 +7043,13 @@
     </row>
     <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -7059,13 +7077,13 @@
     </row>
     <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -7093,13 +7111,13 @@
     </row>
     <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -7127,13 +7145,13 @@
     </row>
     <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -7161,13 +7179,13 @@
     </row>
     <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -7195,13 +7213,13 @@
     </row>
     <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -7229,13 +7247,13 @@
     </row>
     <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
@@ -7263,13 +7281,13 @@
     </row>
     <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B143" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
@@ -7297,13 +7315,13 @@
     </row>
     <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -7331,13 +7349,13 @@
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -7365,13 +7383,13 @@
     </row>
     <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -7399,13 +7417,13 @@
     </row>
     <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -7433,13 +7451,13 @@
     </row>
     <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -7467,13 +7485,13 @@
     </row>
     <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -7501,13 +7519,13 @@
     </row>
     <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -7535,13 +7553,13 @@
     </row>
     <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
@@ -7569,13 +7587,13 @@
     </row>
     <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -7603,13 +7621,13 @@
     </row>
     <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
@@ -7637,13 +7655,13 @@
     </row>
     <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
@@ -7671,13 +7689,13 @@
     </row>
     <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
@@ -7705,13 +7723,13 @@
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
@@ -7739,13 +7757,13 @@
     </row>
     <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
@@ -7773,13 +7791,13 @@
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
@@ -7807,13 +7825,13 @@
     </row>
     <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
@@ -7841,13 +7859,13 @@
     </row>
     <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="3" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -7875,13 +7893,13 @@
     </row>
     <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
@@ -7909,13 +7927,13 @@
     </row>
     <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
@@ -7943,13 +7961,13 @@
     </row>
     <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
@@ -7977,13 +7995,13 @@
     </row>
     <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
@@ -8011,13 +8029,13 @@
     </row>
     <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B165" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
@@ -8045,13 +8063,13 @@
     </row>
     <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
@@ -8079,13 +8097,13 @@
     </row>
     <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
@@ -8113,13 +8131,13 @@
     </row>
     <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
@@ -8147,13 +8165,13 @@
     </row>
     <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
@@ -8181,13 +8199,13 @@
     </row>
     <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
@@ -8215,13 +8233,13 @@
     </row>
     <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
@@ -8249,13 +8267,13 @@
     </row>
     <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
@@ -8283,13 +8301,13 @@
     </row>
     <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
@@ -8317,13 +8335,13 @@
     </row>
     <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
@@ -8351,13 +8369,13 @@
     </row>
     <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
@@ -8385,13 +8403,13 @@
     </row>
     <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B176" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
@@ -8419,13 +8437,13 @@
     </row>
     <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="3" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
@@ -8453,13 +8471,13 @@
     </row>
     <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="3" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
@@ -8487,13 +8505,13 @@
     </row>
     <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
@@ -8521,13 +8539,13 @@
     </row>
     <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
@@ -8555,13 +8573,13 @@
     </row>
     <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -8589,13 +8607,13 @@
     </row>
     <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -8623,13 +8641,13 @@
     </row>
     <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -8657,13 +8675,13 @@
     </row>
     <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -8691,13 +8709,13 @@
     </row>
     <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -8725,13 +8743,13 @@
     </row>
     <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -8759,13 +8777,13 @@
     </row>
     <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B187" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C187" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -8793,13 +8811,13 @@
     </row>
     <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -8827,13 +8845,13 @@
     </row>
     <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -8861,13 +8879,13 @@
     </row>
     <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -8895,13 +8913,13 @@
     </row>
     <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -8929,13 +8947,13 @@
     </row>
     <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -8963,13 +8981,13 @@
     </row>
     <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -8997,13 +9015,13 @@
     </row>
     <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -9031,13 +9049,13 @@
     </row>
     <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -9065,13 +9083,13 @@
     </row>
     <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -9099,13 +9117,13 @@
     </row>
     <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="3" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -9133,13 +9151,13 @@
     </row>
     <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -9167,13 +9185,13 @@
     </row>
     <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="3" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -9201,13 +9219,13 @@
     </row>
     <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -9235,13 +9253,13 @@
     </row>
     <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="3" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -9269,13 +9287,13 @@
     </row>
     <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
@@ -9303,13 +9321,13 @@
     </row>
     <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="3" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
@@ -9337,13 +9355,13 @@
     </row>
     <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="3" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -9371,13 +9389,13 @@
     </row>
     <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -9405,13 +9423,13 @@
     </row>
     <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="3" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -9439,13 +9457,13 @@
     </row>
     <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="3" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -9473,13 +9491,13 @@
     </row>
     <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -9507,13 +9525,13 @@
     </row>
     <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="3" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B209" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C209" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -9541,13 +9559,13 @@
     </row>
     <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -9575,13 +9593,13 @@
     </row>
     <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -9609,13 +9627,13 @@
     </row>
     <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -9643,13 +9661,13 @@
     </row>
     <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="3" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -9677,13 +9695,13 @@
     </row>
     <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="3" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -9711,13 +9729,13 @@
     </row>
     <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="3" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -9745,13 +9763,13 @@
     </row>
     <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="3" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -9779,13 +9797,13 @@
     </row>
     <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -9813,13 +9831,13 @@
     </row>
     <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -9847,13 +9865,13 @@
     </row>
     <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -9881,13 +9899,13 @@
     </row>
     <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B220" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C220" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -9915,13 +9933,13 @@
     </row>
     <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -9949,13 +9967,13 @@
     </row>
     <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="3" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -9983,13 +10001,13 @@
     </row>
     <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="3" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -10017,13 +10035,13 @@
     </row>
     <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="3" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -10051,13 +10069,13 @@
     </row>
     <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="3" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -10085,13 +10103,13 @@
     </row>
     <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -10119,13 +10137,13 @@
     </row>
     <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
@@ -10153,13 +10171,13 @@
     </row>
     <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="3" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -10187,13 +10205,13 @@
     </row>
     <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="3" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -10221,13 +10239,13 @@
     </row>
     <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="3" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -10255,13 +10273,13 @@
     </row>
     <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="3" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
@@ -10289,13 +10307,13 @@
     </row>
     <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="3" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -10323,13 +10341,13 @@
     </row>
     <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="3" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -10357,13 +10375,13 @@
     </row>
     <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="3" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -10391,13 +10409,13 @@
     </row>
     <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="3" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
@@ -10425,13 +10443,13 @@
     </row>
     <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="3" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -10459,13 +10477,13 @@
     </row>
     <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="3" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -10493,13 +10511,13 @@
     </row>
     <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="3" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
@@ -10527,13 +10545,13 @@
     </row>
     <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="3" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
@@ -10561,13 +10579,13 @@
     </row>
     <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="3" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
@@ -10595,13 +10613,13 @@
     </row>
     <row r="241" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="3" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
@@ -10629,13 +10647,13 @@
     </row>
     <row r="242" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="3" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
@@ -10663,13 +10681,13 @@
     </row>
     <row r="243" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="3" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
@@ -10697,13 +10715,13 @@
     </row>
     <row r="244" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
@@ -10731,13 +10749,13 @@
     </row>
     <row r="245" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
@@ -10765,13 +10783,13 @@
     </row>
     <row r="246" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="3" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
@@ -10799,13 +10817,13 @@
     </row>
     <row r="247" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="3" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
@@ -10833,13 +10851,13 @@
     </row>
     <row r="248" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="3" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
@@ -10867,13 +10885,13 @@
     </row>
     <row r="249" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="3" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
@@ -10901,13 +10919,13 @@
     </row>
     <row r="250" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
@@ -10935,13 +10953,13 @@
     </row>
     <row r="251" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="3" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
@@ -10969,13 +10987,13 @@
     </row>
     <row r="252" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="3" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
@@ -11003,13 +11021,13 @@
     </row>
     <row r="253" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
@@ -11037,13 +11055,13 @@
     </row>
     <row r="254" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
@@ -11071,13 +11089,13 @@
     </row>
     <row r="255" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
@@ -11105,13 +11123,13 @@
     </row>
     <row r="256" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
@@ -11139,13 +11157,13 @@
     </row>
     <row r="257" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="3" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
@@ -11173,13 +11191,13 @@
     </row>
     <row r="258" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="3" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
@@ -11207,13 +11225,13 @@
     </row>
     <row r="259" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
@@ -11241,13 +11259,13 @@
     </row>
     <row r="260" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
@@ -11275,13 +11293,13 @@
     </row>
     <row r="261" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
@@ -11309,13 +11327,13 @@
     </row>
     <row r="262" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
@@ -11343,13 +11361,13 @@
     </row>
     <row r="263" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
@@ -11377,13 +11395,13 @@
     </row>
     <row r="264" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
@@ -11411,13 +11429,13 @@
     </row>
     <row r="265" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
@@ -11445,13 +11463,13 @@
     </row>
     <row r="266" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
@@ -11479,13 +11497,13 @@
     </row>
     <row r="267" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
@@ -11513,13 +11531,13 @@
     </row>
     <row r="268" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
@@ -11547,13 +11565,13 @@
     </row>
     <row r="269" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
@@ -11581,13 +11599,13 @@
     </row>
     <row r="270" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
@@ -11615,13 +11633,13 @@
     </row>
     <row r="271" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
@@ -11649,13 +11667,13 @@
     </row>
     <row r="272" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
@@ -11683,13 +11701,13 @@
     </row>
     <row r="273" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="1" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
@@ -11717,13 +11735,13 @@
     </row>
     <row r="274" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
@@ -11751,13 +11769,13 @@
     </row>
     <row r="275" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
@@ -11785,13 +11803,13 @@
     </row>
     <row r="276" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
@@ -11819,13 +11837,13 @@
     </row>
     <row r="277" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
@@ -11853,13 +11871,13 @@
     </row>
     <row r="278" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
@@ -11887,13 +11905,13 @@
     </row>
     <row r="279" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="1" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
@@ -11921,13 +11939,13 @@
     </row>
     <row r="280" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
@@ -11955,13 +11973,13 @@
     </row>
     <row r="281" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
@@ -11989,13 +12007,13 @@
     </row>
     <row r="282" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
@@ -12023,13 +12041,13 @@
     </row>
     <row r="283" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
@@ -12057,13 +12075,13 @@
     </row>
     <row r="284" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
@@ -12091,13 +12109,13 @@
     </row>
     <row r="285" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
@@ -12125,13 +12143,13 @@
     </row>
     <row r="286" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
@@ -12159,13 +12177,13 @@
     </row>
     <row r="287" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
@@ -12193,13 +12211,13 @@
     </row>
     <row r="288" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288" s="1" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
@@ -12227,13 +12245,13 @@
     </row>
     <row r="289" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
@@ -12261,13 +12279,13 @@
     </row>
     <row r="290" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
@@ -12295,13 +12313,13 @@
     </row>
     <row r="291" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
@@ -12329,13 +12347,13 @@
     </row>
     <row r="292" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="1" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
@@ -12363,13 +12381,13 @@
     </row>
     <row r="293" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
@@ -12397,13 +12415,13 @@
     </row>
     <row r="294" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
@@ -12431,13 +12449,13 @@
     </row>
     <row r="295" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
@@ -12465,13 +12483,13 @@
     </row>
     <row r="296" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
@@ -12499,13 +12517,13 @@
     </row>
     <row r="297" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297" s="1" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
@@ -12533,13 +12551,13 @@
     </row>
     <row r="298" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
@@ -12567,13 +12585,13 @@
     </row>
     <row r="299" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
@@ -12601,13 +12619,13 @@
     </row>
     <row r="300" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
@@ -12635,13 +12653,13 @@
     </row>
     <row r="301" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
@@ -12669,13 +12687,13 @@
     </row>
     <row r="302" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
@@ -12703,13 +12721,13 @@
     </row>
     <row r="303" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
@@ -12737,13 +12755,13 @@
     </row>
     <row r="304" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
@@ -12771,13 +12789,13 @@
     </row>
     <row r="305" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
@@ -12805,13 +12823,13 @@
     </row>
     <row r="306" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
@@ -12839,13 +12857,13 @@
     </row>
     <row r="307" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
@@ -12873,13 +12891,13 @@
     </row>
     <row r="308" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
@@ -12907,13 +12925,13 @@
     </row>
     <row r="309" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
@@ -12941,13 +12959,13 @@
     </row>
     <row r="310" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
@@ -12975,13 +12993,13 @@
     </row>
     <row r="311" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
@@ -13009,13 +13027,13 @@
     </row>
     <row r="312" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
@@ -13043,13 +13061,13 @@
     </row>
     <row r="313" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
@@ -13077,13 +13095,13 @@
     </row>
     <row r="314" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="1" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
@@ -13111,13 +13129,13 @@
     </row>
     <row r="315" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
@@ -13145,13 +13163,13 @@
     </row>
     <row r="316" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
@@ -13179,13 +13197,13 @@
     </row>
     <row r="317" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
@@ -13213,13 +13231,13 @@
     </row>
     <row r="318" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="3" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
@@ -13247,13 +13265,13 @@
     </row>
     <row r="319" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="3" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
@@ -13281,13 +13299,13 @@
     </row>
     <row r="320" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="3" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
@@ -13315,13 +13333,13 @@
     </row>
     <row r="321" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="3" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
@@ -13349,13 +13367,13 @@
     </row>
     <row r="322" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322" s="3" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
@@ -13383,13 +13401,13 @@
     </row>
     <row r="323" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323" s="3" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
@@ -13417,13 +13435,13 @@
     </row>
     <row r="324" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="3" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
@@ -13451,13 +13469,13 @@
     </row>
     <row r="325" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="3" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
@@ -13485,13 +13503,13 @@
     </row>
     <row r="326" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="3" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
@@ -13519,13 +13537,13 @@
     </row>
     <row r="327" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="3" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
@@ -13553,13 +13571,13 @@
     </row>
     <row r="328" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="3" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
@@ -13587,13 +13605,13 @@
     </row>
     <row r="329" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="3" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
@@ -13621,13 +13639,13 @@
     </row>
     <row r="330" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="3" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
@@ -13655,13 +13673,13 @@
     </row>
     <row r="331" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="3" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
@@ -13689,13 +13707,13 @@
     </row>
     <row r="332" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="3" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
@@ -13723,13 +13741,13 @@
     </row>
     <row r="333" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A333" s="3" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
@@ -13757,13 +13775,13 @@
     </row>
     <row r="334" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="3" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
@@ -13791,13 +13809,13 @@
     </row>
     <row r="335" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="3" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
@@ -13825,13 +13843,13 @@
     </row>
     <row r="336" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="3" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
@@ -13859,13 +13877,13 @@
     </row>
     <row r="337" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="3" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
@@ -13893,13 +13911,13 @@
     </row>
     <row r="338" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="3" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
@@ -13927,13 +13945,13 @@
     </row>
     <row r="339" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="3" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
@@ -13961,13 +13979,13 @@
     </row>
     <row r="340" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="3" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
@@ -13995,13 +14013,13 @@
     </row>
     <row r="341" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A341" s="3" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
@@ -14029,13 +14047,13 @@
     </row>
     <row r="342" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="3" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
@@ -14063,13 +14081,13 @@
     </row>
     <row r="343" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="3" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
@@ -14097,13 +14115,13 @@
     </row>
     <row r="344" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="3" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
@@ -14131,13 +14149,13 @@
     </row>
     <row r="345" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="3" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
@@ -14165,13 +14183,13 @@
     </row>
     <row r="346" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="3" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
@@ -14199,13 +14217,13 @@
     </row>
     <row r="347" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="3" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
@@ -14233,13 +14251,13 @@
     </row>
     <row r="348" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="3" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
@@ -14267,13 +14285,13 @@
     </row>
     <row r="349" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="3" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
@@ -14301,13 +14319,13 @@
     </row>
     <row r="350" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="3" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
@@ -14335,13 +14353,13 @@
     </row>
     <row r="351" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="3" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
@@ -14369,13 +14387,13 @@
     </row>
     <row r="352" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="3" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
@@ -14403,13 +14421,13 @@
     </row>
     <row r="353" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353" s="3" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
@@ -14437,13 +14455,13 @@
     </row>
     <row r="354" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
@@ -14471,13 +14489,13 @@
     </row>
     <row r="355" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="3" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
@@ -14505,13 +14523,13 @@
     </row>
     <row r="356" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="3" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
@@ -14539,13 +14557,13 @@
     </row>
     <row r="357" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="3" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
@@ -14573,13 +14591,13 @@
     </row>
     <row r="358" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="3" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
@@ -14607,13 +14625,13 @@
     </row>
     <row r="359" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="3" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
@@ -14641,13 +14659,13 @@
     </row>
     <row r="360" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="3" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
@@ -14675,13 +14693,13 @@
     </row>
     <row r="361" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="3" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
@@ -14709,13 +14727,13 @@
     </row>
     <row r="362" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="3" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
@@ -14743,13 +14761,13 @@
     </row>
     <row r="363" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="3" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
@@ -14777,13 +14795,13 @@
     </row>
     <row r="364" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="3" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D364" s="1"/>
       <c r="E364" s="1"/>
@@ -14811,13 +14829,13 @@
     </row>
     <row r="365" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="3" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D365" s="1"/>
       <c r="E365" s="1"/>
@@ -14845,13 +14863,13 @@
     </row>
     <row r="366" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A366" s="3" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D366" s="1"/>
       <c r="E366" s="1"/>
@@ -14879,13 +14897,13 @@
     </row>
     <row r="367" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A367" s="3" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D367" s="1"/>
       <c r="E367" s="1"/>
@@ -14913,13 +14931,13 @@
     </row>
     <row r="368" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
@@ -14947,13 +14965,13 @@
     </row>
     <row r="369" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="3" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
@@ -14981,13 +14999,13 @@
     </row>
     <row r="370" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="3" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D370" s="1"/>
       <c r="E370" s="1"/>
@@ -15015,13 +15033,13 @@
     </row>
     <row r="371" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="3" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D371" s="1"/>
       <c r="E371" s="1"/>
@@ -15049,13 +15067,13 @@
     </row>
     <row r="372" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A372" s="3" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
@@ -15083,13 +15101,13 @@
     </row>
     <row r="373" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="3" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D373" s="1"/>
       <c r="E373" s="1"/>
@@ -15117,13 +15135,13 @@
     </row>
     <row r="374" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="3" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
@@ -15151,13 +15169,13 @@
     </row>
     <row r="375" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
@@ -15185,13 +15203,13 @@
     </row>
     <row r="376" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="3" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
@@ -15219,13 +15237,13 @@
     </row>
     <row r="377" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="3" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
@@ -15253,13 +15271,13 @@
     </row>
     <row r="378" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="3" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
@@ -15287,13 +15305,13 @@
     </row>
     <row r="379" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="3" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
@@ -15321,13 +15339,13 @@
     </row>
     <row r="380" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="3" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
@@ -15355,13 +15373,13 @@
     </row>
     <row r="381" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="3" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D381" s="1"/>
       <c r="E381" s="1"/>
@@ -15389,13 +15407,13 @@
     </row>
     <row r="382" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="3" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
@@ -15423,13 +15441,13 @@
     </row>
     <row r="383" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="3" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
@@ -15457,13 +15475,13 @@
     </row>
     <row r="384" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="3" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
@@ -15491,13 +15509,13 @@
     </row>
     <row r="385" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="3" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
@@ -15525,13 +15543,13 @@
     </row>
     <row r="386" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="3" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
@@ -15559,13 +15577,13 @@
     </row>
     <row r="387" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="3" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
@@ -15593,13 +15611,13 @@
     </row>
     <row r="388" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="3" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
@@ -15627,13 +15645,13 @@
     </row>
     <row r="389" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="3" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D389" s="1"/>
       <c r="E389" s="1"/>
@@ -15661,13 +15679,13 @@
     </row>
     <row r="390" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="3" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D390" s="1"/>
       <c r="E390" s="1"/>
@@ -15695,13 +15713,13 @@
     </row>
     <row r="391" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="3" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D391" s="1"/>
       <c r="E391" s="1"/>
@@ -15729,13 +15747,13 @@
     </row>
     <row r="392" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="3" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D392" s="1"/>
       <c r="E392" s="1"/>
@@ -15763,13 +15781,13 @@
     </row>
     <row r="393" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="3" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D393" s="1"/>
       <c r="E393" s="1"/>
@@ -15797,13 +15815,13 @@
     </row>
     <row r="394" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="3" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D394" s="1"/>
       <c r="E394" s="1"/>
@@ -15831,13 +15849,13 @@
     </row>
     <row r="395" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="3" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D395" s="1"/>
       <c r="E395" s="1"/>
@@ -15865,13 +15883,13 @@
     </row>
     <row r="396" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="3" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D396" s="1"/>
       <c r="E396" s="1"/>
@@ -15899,13 +15917,13 @@
     </row>
     <row r="397" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="3" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D397" s="1"/>
       <c r="E397" s="1"/>
@@ -15933,13 +15951,13 @@
     </row>
     <row r="398" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="3" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D398" s="1"/>
       <c r="E398" s="1"/>
@@ -15967,13 +15985,13 @@
     </row>
     <row r="399" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="3" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D399" s="1"/>
       <c r="E399" s="1"/>
@@ -16001,13 +16019,13 @@
     </row>
     <row r="400" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="3" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
@@ -16035,13 +16053,13 @@
     </row>
     <row r="401" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="3" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
@@ -16069,13 +16087,13 @@
     </row>
     <row r="402" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="3" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D402" s="1"/>
       <c r="E402" s="1"/>
@@ -16103,13 +16121,13 @@
     </row>
     <row r="403" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="3" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D403" s="1"/>
       <c r="E403" s="1"/>
@@ -16137,13 +16155,13 @@
     </row>
     <row r="404" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="3" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D404" s="1"/>
       <c r="E404" s="1"/>
@@ -16171,13 +16189,13 @@
     </row>
     <row r="405" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="3" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D405" s="1"/>
       <c r="E405" s="1"/>
@@ -16205,13 +16223,13 @@
     </row>
     <row r="406" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="3" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D406" s="1"/>
       <c r="E406" s="1"/>
@@ -16239,13 +16257,13 @@
     </row>
     <row r="407" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="3" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D407" s="1"/>
       <c r="E407" s="1"/>
@@ -16273,13 +16291,13 @@
     </row>
     <row r="408" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="3" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D408" s="1"/>
       <c r="E408" s="1"/>
@@ -16307,13 +16325,13 @@
     </row>
     <row r="409" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D409" s="1"/>
       <c r="E409" s="1"/>
@@ -16341,13 +16359,13 @@
     </row>
     <row r="410" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D410" s="1"/>
       <c r="E410" s="1"/>
@@ -16375,13 +16393,13 @@
     </row>
     <row r="411" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D411" s="1"/>
       <c r="E411" s="1"/>
@@ -16409,13 +16427,13 @@
     </row>
     <row r="412" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="3" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D412" s="1"/>
       <c r="E412" s="1"/>
@@ -16443,13 +16461,13 @@
     </row>
     <row r="413" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D413" s="1"/>
       <c r="E413" s="1"/>
@@ -16477,13 +16495,13 @@
     </row>
     <row r="414" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="3" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D414" s="1"/>
       <c r="E414" s="1"/>
@@ -16511,13 +16529,13 @@
     </row>
     <row r="415" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="3" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D415" s="1"/>
       <c r="E415" s="1"/>
@@ -16545,13 +16563,13 @@
     </row>
     <row r="416" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="3" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D416" s="1"/>
       <c r="E416" s="1"/>
@@ -16579,13 +16597,13 @@
     </row>
     <row r="417" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="3" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D417" s="1"/>
       <c r="E417" s="1"/>
@@ -16613,13 +16631,13 @@
     </row>
     <row r="418" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="3" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D418" s="1"/>
       <c r="E418" s="1"/>
@@ -16647,13 +16665,13 @@
     </row>
     <row r="419" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D419" s="1"/>
       <c r="E419" s="1"/>
@@ -16681,13 +16699,13 @@
     </row>
     <row r="420" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="3" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D420" s="1"/>
       <c r="E420" s="1"/>
@@ -16715,13 +16733,13 @@
     </row>
     <row r="421" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="3" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D421" s="1"/>
       <c r="E421" s="1"/>
@@ -16749,13 +16767,13 @@
     </row>
     <row r="422" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="3" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D422" s="1"/>
       <c r="E422" s="1"/>
@@ -16783,13 +16801,13 @@
     </row>
     <row r="423" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="3" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D423" s="1"/>
       <c r="E423" s="1"/>
@@ -16817,13 +16835,13 @@
     </row>
     <row r="424" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="3" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D424" s="1"/>
       <c r="E424" s="1"/>
@@ -16851,13 +16869,13 @@
     </row>
     <row r="425" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="3" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D425" s="1"/>
       <c r="E425" s="1"/>
@@ -16885,13 +16903,13 @@
     </row>
     <row r="426" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426" s="3" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D426" s="1"/>
       <c r="E426" s="1"/>
@@ -16919,13 +16937,13 @@
     </row>
     <row r="427" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="3" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D427" s="1"/>
       <c r="E427" s="1"/>
@@ -16953,13 +16971,13 @@
     </row>
     <row r="428" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="3" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D428" s="1"/>
       <c r="E428" s="1"/>
@@ -16987,13 +17005,13 @@
     </row>
     <row r="429" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="3" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D429" s="1"/>
       <c r="E429" s="1"/>
@@ -17021,13 +17039,13 @@
     </row>
     <row r="430" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="3" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D430" s="1"/>
       <c r="E430" s="1"/>
@@ -17055,13 +17073,13 @@
     </row>
     <row r="431" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="3" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D431" s="1"/>
       <c r="E431" s="1"/>
@@ -17089,13 +17107,13 @@
     </row>
     <row r="432" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="3" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D432" s="1"/>
       <c r="E432" s="1"/>
@@ -17123,13 +17141,13 @@
     </row>
     <row r="433" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="3" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D433" s="1"/>
       <c r="E433" s="1"/>
@@ -17157,13 +17175,13 @@
     </row>
     <row r="434" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="3" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D434" s="1"/>
       <c r="E434" s="1"/>
@@ -17191,13 +17209,13 @@
     </row>
     <row r="435" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="3" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D435" s="1"/>
       <c r="E435" s="1"/>
@@ -17225,10 +17243,10 @@
     </row>
     <row r="436" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="1" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C436" s="1"/>
       <c r="D436" s="1"/>
@@ -17257,10 +17275,10 @@
     </row>
     <row r="437" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="1" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C437" s="1"/>
       <c r="D437" s="1"/>
@@ -17289,10 +17307,10 @@
     </row>
     <row r="438" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="1" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C438" s="1"/>
       <c r="D438" s="1"/>
@@ -17321,10 +17339,10 @@
     </row>
     <row r="439" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="3" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C439" s="1"/>
       <c r="D439" s="1"/>
@@ -17353,10 +17371,10 @@
     </row>
     <row r="440" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="3" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C440" s="1"/>
       <c r="D440" s="1"/>
@@ -17385,10 +17403,10 @@
     </row>
     <row r="441" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="3" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C441" s="1"/>
       <c r="D441" s="1"/>
@@ -17417,10 +17435,10 @@
     </row>
     <row r="442" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="3" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C442" s="1"/>
       <c r="D442" s="1"/>
@@ -17449,10 +17467,10 @@
     </row>
     <row r="443" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="3" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C443" s="1"/>
       <c r="D443" s="1"/>
@@ -17481,10 +17499,10 @@
     </row>
     <row r="444" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A444" s="3" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C444" s="1"/>
       <c r="D444" s="1"/>
@@ -17513,10 +17531,10 @@
     </row>
     <row r="445" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A445" s="3" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C445" s="1"/>
       <c r="D445" s="1"/>
@@ -17545,10 +17563,10 @@
     </row>
     <row r="446" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A446" s="3" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C446" s="1"/>
       <c r="D446" s="1"/>
@@ -17577,10 +17595,10 @@
     </row>
     <row r="447" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A447" s="3" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C447" s="1"/>
       <c r="D447" s="1"/>
@@ -17609,10 +17627,10 @@
     </row>
     <row r="448" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A448" s="3" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C448" s="1"/>
       <c r="D448" s="1"/>
@@ -17641,10 +17659,10 @@
     </row>
     <row r="449" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A449" s="3" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C449" s="1"/>
       <c r="D449" s="1"/>
@@ -17673,10 +17691,10 @@
     </row>
     <row r="450" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A450" s="3" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C450" s="1"/>
       <c r="D450" s="1"/>
@@ -17705,10 +17723,10 @@
     </row>
     <row r="451" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A451" s="3" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C451" s="1"/>
       <c r="D451" s="1"/>
@@ -17737,10 +17755,10 @@
     </row>
     <row r="452" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="1" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C452" s="1"/>
       <c r="D452" s="1"/>
@@ -17769,10 +17787,10 @@
     </row>
     <row r="453" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A453" s="3" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C453" s="1"/>
       <c r="D453" s="1"/>
@@ -17801,10 +17819,10 @@
     </row>
     <row r="454" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A454" s="1" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C454" s="1"/>
       <c r="D454" s="1"/>
@@ -17833,10 +17851,10 @@
     </row>
     <row r="455" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A455" s="3" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C455" s="1"/>
       <c r="D455" s="1"/>
@@ -17865,10 +17883,10 @@
     </row>
     <row r="456" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A456" s="3" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="C456" s="1"/>
       <c r="D456" s="1"/>
@@ -17897,10 +17915,10 @@
     </row>
     <row r="457" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A457" s="3" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C457" s="1"/>
       <c r="D457" s="1"/>
@@ -17929,10 +17947,10 @@
     </row>
     <row r="458" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A458" s="3" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C458" s="1"/>
       <c r="D458" s="1"/>
@@ -17961,10 +17979,10 @@
     </row>
     <row r="459" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A459" s="3" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C459" s="1"/>
       <c r="D459" s="1"/>
@@ -17993,10 +18011,10 @@
     </row>
     <row r="460" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A460" s="3" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C460" s="1"/>
       <c r="D460" s="1"/>
@@ -18025,10 +18043,10 @@
     </row>
     <row r="461" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A461" s="3" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C461" s="1"/>
       <c r="D461" s="1"/>
@@ -18057,10 +18075,10 @@
     </row>
     <row r="462" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A462" s="3" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C462" s="1"/>
       <c r="D462" s="1"/>
@@ -18089,10 +18107,10 @@
     </row>
     <row r="463" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A463" s="1" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="C463" s="1"/>
       <c r="D463" s="1"/>
@@ -18121,10 +18139,10 @@
     </row>
     <row r="464" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A464" s="1" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C464" s="1"/>
       <c r="D464" s="1"/>
@@ -18153,10 +18171,10 @@
     </row>
     <row r="465" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="1" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C465" s="1"/>
       <c r="D465" s="1"/>
@@ -18185,10 +18203,10 @@
     </row>
     <row r="466" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="1" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C466" s="1"/>
       <c r="D466" s="1"/>
@@ -18217,10 +18235,10 @@
     </row>
     <row r="467" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="1" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C467" s="1"/>
       <c r="D467" s="1"/>
@@ -18249,10 +18267,10 @@
     </row>
     <row r="468" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="1" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C468" s="1"/>
       <c r="D468" s="1"/>
@@ -18313,10 +18331,10 @@
     </row>
     <row r="470" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="1" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C470" s="1"/>
       <c r="D470" s="1"/>
@@ -18345,10 +18363,10 @@
     </row>
     <row r="471" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C471" s="1"/>
       <c r="D471" s="1"/>
@@ -18377,10 +18395,10 @@
     </row>
     <row r="472" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="1" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C472" s="1"/>
       <c r="D472" s="1"/>
@@ -18409,10 +18427,10 @@
     </row>
     <row r="473" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="1" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C473" s="1"/>
       <c r="D473" s="1"/>
@@ -18441,10 +18459,10 @@
     </row>
     <row r="474" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="1" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C474" s="1"/>
       <c r="D474" s="1"/>
@@ -18473,10 +18491,10 @@
     </row>
     <row r="475" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="1" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="C475" s="1"/>
       <c r="D475" s="1"/>
@@ -33265,7 +33283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB4F074-3897-FD42-B912-CC5B2559E3CA}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
@@ -33287,6 +33305,54 @@
       </c>
       <c r="B3" s="1" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>716</v>
       </c>
     </row>
   </sheetData>
@@ -33334,45 +33400,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B960C9-C524-4C4D-8262-74CAEBE3E241}">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CD247F-14DB-8744-B19A-4D3A306027D6}">
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1234</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tool/chem.xlsx
+++ b/tool/chem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pp/Desktop/CS_SWU_68/CP242/organic-chem-app/tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78C34E8-84F2-9E46-A07B-D497BE64F786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{653D174C-5CC2-B24B-8602-944A277EC37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="724">
   <si>
     <t>molecularFormula</t>
   </si>
@@ -292,6 +292,24 @@
     <t>Δ</t>
   </si>
   <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
     <t>Chemical</t>
   </si>
   <si>
@@ -2174,6 +2192,9 @@
   </si>
   <si>
     <t>ปฏิกิรยาไฮโดรไลซิสของเอไมด์</t>
+  </si>
+  <si>
+    <t>name</t>
   </si>
 </sst>
 </file>
@@ -2459,7 +2480,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1"/>
@@ -2929,10 +2950,10 @@
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>73</v>
@@ -2963,10 +2984,10 @@
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>73</v>
@@ -2997,10 +3018,10 @@
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>73</v>
@@ -3031,10 +3052,10 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>73</v>
@@ -3065,10 +3086,10 @@
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>73</v>
@@ -3099,10 +3120,10 @@
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>73</v>
@@ -3133,10 +3154,10 @@
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>73</v>
@@ -3167,10 +3188,10 @@
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>73</v>
@@ -3201,10 +3222,10 @@
     </row>
     <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>73</v>
@@ -3235,10 +3256,10 @@
     </row>
     <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>73</v>
@@ -3269,10 +3290,10 @@
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>73</v>
@@ -3303,10 +3324,10 @@
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>73</v>
@@ -3337,10 +3358,10 @@
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>73</v>
@@ -3371,10 +3392,10 @@
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>73</v>
@@ -3405,10 +3426,10 @@
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>73</v>
@@ -3439,10 +3460,10 @@
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>73</v>
@@ -3473,10 +3494,10 @@
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>73</v>
@@ -3507,10 +3528,10 @@
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>73</v>
@@ -3541,10 +3562,10 @@
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>73</v>
@@ -3575,10 +3596,10 @@
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>73</v>
@@ -3609,10 +3630,10 @@
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>73</v>
@@ -3643,10 +3664,10 @@
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>73</v>
@@ -3677,10 +3698,10 @@
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>73</v>
@@ -3711,10 +3732,10 @@
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>73</v>
@@ -3745,10 +3766,10 @@
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>73</v>
@@ -3779,10 +3800,10 @@
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>73</v>
@@ -3813,10 +3834,10 @@
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>73</v>
@@ -3847,10 +3868,10 @@
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>73</v>
@@ -3881,10 +3902,10 @@
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>73</v>
@@ -3915,10 +3936,10 @@
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>73</v>
@@ -3949,10 +3970,10 @@
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>73</v>
@@ -3983,10 +4004,10 @@
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>73</v>
@@ -4017,10 +4038,10 @@
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>73</v>
@@ -4051,10 +4072,10 @@
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>73</v>
@@ -4085,10 +4106,10 @@
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>74</v>
@@ -4119,10 +4140,10 @@
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>74</v>
@@ -4153,10 +4174,10 @@
     </row>
     <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>74</v>
@@ -4187,10 +4208,10 @@
     </row>
     <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>74</v>
@@ -4221,10 +4242,10 @@
     </row>
     <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>74</v>
@@ -4255,10 +4276,10 @@
     </row>
     <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>74</v>
@@ -4289,10 +4310,10 @@
     </row>
     <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>74</v>
@@ -4323,10 +4344,10 @@
     </row>
     <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>74</v>
@@ -4357,10 +4378,10 @@
     </row>
     <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>74</v>
@@ -4391,10 +4412,10 @@
     </row>
     <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>74</v>
@@ -4425,10 +4446,10 @@
     </row>
     <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>74</v>
@@ -5241,10 +5262,10 @@
     </row>
     <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>76</v>
@@ -5275,13 +5296,13 @@
     </row>
     <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -5309,13 +5330,13 @@
     </row>
     <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -5343,13 +5364,13 @@
     </row>
     <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -5377,13 +5398,13 @@
     </row>
     <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -5411,13 +5432,13 @@
     </row>
     <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -5445,13 +5466,13 @@
     </row>
     <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -5479,13 +5500,13 @@
     </row>
     <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -5513,13 +5534,13 @@
     </row>
     <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -5547,13 +5568,13 @@
     </row>
     <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
@@ -5581,13 +5602,13 @@
     </row>
     <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -5615,13 +5636,13 @@
     </row>
     <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -5649,13 +5670,13 @@
     </row>
     <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
@@ -5683,13 +5704,13 @@
     </row>
     <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
@@ -5717,13 +5738,13 @@
     </row>
     <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
@@ -5751,13 +5772,13 @@
     </row>
     <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
@@ -5785,13 +5806,13 @@
     </row>
     <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
@@ -5819,13 +5840,13 @@
     </row>
     <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
@@ -5853,13 +5874,13 @@
     </row>
     <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
@@ -5887,13 +5908,13 @@
     </row>
     <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
@@ -5921,13 +5942,13 @@
     </row>
     <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -5955,13 +5976,13 @@
     </row>
     <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
@@ -5989,13 +6010,13 @@
     </row>
     <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
@@ -6023,13 +6044,13 @@
     </row>
     <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -6057,13 +6078,13 @@
     </row>
     <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -6091,13 +6112,13 @@
     </row>
     <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
@@ -6125,13 +6146,13 @@
     </row>
     <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -6159,13 +6180,13 @@
     </row>
     <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -6193,13 +6214,13 @@
     </row>
     <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
@@ -6227,13 +6248,13 @@
     </row>
     <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
@@ -6261,13 +6282,13 @@
     </row>
     <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
@@ -6295,13 +6316,13 @@
     </row>
     <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
@@ -6329,13 +6350,13 @@
     </row>
     <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
@@ -6363,13 +6384,13 @@
     </row>
     <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -6397,13 +6418,13 @@
     </row>
     <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -6431,13 +6452,13 @@
     </row>
     <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -6465,13 +6486,13 @@
     </row>
     <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -6499,13 +6520,13 @@
     </row>
     <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -6533,13 +6554,13 @@
     </row>
     <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -6567,13 +6588,13 @@
     </row>
     <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -6601,13 +6622,13 @@
     </row>
     <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -6635,13 +6656,13 @@
     </row>
     <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -6669,13 +6690,13 @@
     </row>
     <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -6703,13 +6724,13 @@
     </row>
     <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -6737,13 +6758,13 @@
     </row>
     <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -6771,13 +6792,13 @@
     </row>
     <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -6805,13 +6826,13 @@
     </row>
     <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -6839,13 +6860,13 @@
     </row>
     <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -6873,13 +6894,13 @@
     </row>
     <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -6907,13 +6928,13 @@
     </row>
     <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -6941,13 +6962,13 @@
     </row>
     <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -6975,13 +6996,13 @@
     </row>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -7009,13 +7030,13 @@
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -7043,13 +7064,13 @@
     </row>
     <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -7077,13 +7098,13 @@
     </row>
     <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -7111,13 +7132,13 @@
     </row>
     <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -7145,13 +7166,13 @@
     </row>
     <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -7179,13 +7200,13 @@
     </row>
     <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -7213,13 +7234,13 @@
     </row>
     <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -7247,13 +7268,13 @@
     </row>
     <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
@@ -7281,13 +7302,13 @@
     </row>
     <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
@@ -7315,13 +7336,13 @@
     </row>
     <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -7349,13 +7370,13 @@
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -7383,13 +7404,13 @@
     </row>
     <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -7417,13 +7438,13 @@
     </row>
     <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -7451,13 +7472,13 @@
     </row>
     <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -7485,13 +7506,13 @@
     </row>
     <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -7519,13 +7540,13 @@
     </row>
     <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -7553,13 +7574,13 @@
     </row>
     <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
@@ -7587,13 +7608,13 @@
     </row>
     <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -7621,13 +7642,13 @@
     </row>
     <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
@@ -7655,13 +7676,13 @@
     </row>
     <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
@@ -7689,13 +7710,13 @@
     </row>
     <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
@@ -7723,13 +7744,13 @@
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
@@ -7757,13 +7778,13 @@
     </row>
     <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
@@ -7791,13 +7812,13 @@
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
@@ -7825,13 +7846,13 @@
     </row>
     <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
@@ -7859,13 +7880,13 @@
     </row>
     <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -7893,13 +7914,13 @@
     </row>
     <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
@@ -7927,13 +7948,13 @@
     </row>
     <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
@@ -7961,13 +7982,13 @@
     </row>
     <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
@@ -7995,13 +8016,13 @@
     </row>
     <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
@@ -8029,13 +8050,13 @@
     </row>
     <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
@@ -8063,13 +8084,13 @@
     </row>
     <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
@@ -8097,13 +8118,13 @@
     </row>
     <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
@@ -8131,13 +8152,13 @@
     </row>
     <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
@@ -8165,13 +8186,13 @@
     </row>
     <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
@@ -8199,13 +8220,13 @@
     </row>
     <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
@@ -8233,13 +8254,13 @@
     </row>
     <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
@@ -8267,13 +8288,13 @@
     </row>
     <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
@@ -8301,13 +8322,13 @@
     </row>
     <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
@@ -8335,13 +8356,13 @@
     </row>
     <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
@@ -8369,13 +8390,13 @@
     </row>
     <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
@@ -8403,13 +8424,13 @@
     </row>
     <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
@@ -8437,13 +8458,13 @@
     </row>
     <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
@@ -8471,13 +8492,13 @@
     </row>
     <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="3" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
@@ -8505,13 +8526,13 @@
     </row>
     <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="3" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
@@ -8539,13 +8560,13 @@
     </row>
     <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
@@ -8573,13 +8594,13 @@
     </row>
     <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -8607,13 +8628,13 @@
     </row>
     <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -8641,13 +8662,13 @@
     </row>
     <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -8675,13 +8696,13 @@
     </row>
     <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -8709,13 +8730,13 @@
     </row>
     <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -8743,13 +8764,13 @@
     </row>
     <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -8777,13 +8798,13 @@
     </row>
     <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -8811,13 +8832,13 @@
     </row>
     <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -8845,13 +8866,13 @@
     </row>
     <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -8879,13 +8900,13 @@
     </row>
     <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -8913,13 +8934,13 @@
     </row>
     <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -8947,13 +8968,13 @@
     </row>
     <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -8981,13 +9002,13 @@
     </row>
     <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="3" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -9015,13 +9036,13 @@
     </row>
     <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -9049,13 +9070,13 @@
     </row>
     <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -9083,13 +9104,13 @@
     </row>
     <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -9117,13 +9138,13 @@
     </row>
     <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -9151,13 +9172,13 @@
     </row>
     <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -9185,13 +9206,13 @@
     </row>
     <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -9219,13 +9240,13 @@
     </row>
     <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -9253,13 +9274,13 @@
     </row>
     <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -9287,13 +9308,13 @@
     </row>
     <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
@@ -9321,13 +9342,13 @@
     </row>
     <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
@@ -9355,13 +9376,13 @@
     </row>
     <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -9389,13 +9410,13 @@
     </row>
     <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -9423,13 +9444,13 @@
     </row>
     <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -9457,13 +9478,13 @@
     </row>
     <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -9491,13 +9512,13 @@
     </row>
     <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -9525,13 +9546,13 @@
     </row>
     <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -9559,13 +9580,13 @@
     </row>
     <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -9593,13 +9614,13 @@
     </row>
     <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -9627,13 +9648,13 @@
     </row>
     <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -9661,13 +9682,13 @@
     </row>
     <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -9695,13 +9716,13 @@
     </row>
     <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -9729,13 +9750,13 @@
     </row>
     <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -9763,13 +9784,13 @@
     </row>
     <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -9797,13 +9818,13 @@
     </row>
     <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="3" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -9831,13 +9852,13 @@
     </row>
     <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -9865,13 +9886,13 @@
     </row>
     <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -9899,13 +9920,13 @@
     </row>
     <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -9933,13 +9954,13 @@
     </row>
     <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -9967,13 +9988,13 @@
     </row>
     <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -10001,13 +10022,13 @@
     </row>
     <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -10035,13 +10056,13 @@
     </row>
     <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -10069,13 +10090,13 @@
     </row>
     <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -10103,13 +10124,13 @@
     </row>
     <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -10137,13 +10158,13 @@
     </row>
     <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
@@ -10171,13 +10192,13 @@
     </row>
     <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -10205,13 +10226,13 @@
     </row>
     <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -10239,13 +10260,13 @@
     </row>
     <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -10273,13 +10294,13 @@
     </row>
     <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="3" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
@@ -10307,13 +10328,13 @@
     </row>
     <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -10341,13 +10362,13 @@
     </row>
     <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -10375,13 +10396,13 @@
     </row>
     <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -10409,13 +10430,13 @@
     </row>
     <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
@@ -10443,13 +10464,13 @@
     </row>
     <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -10477,13 +10498,13 @@
     </row>
     <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -10511,13 +10532,13 @@
     </row>
     <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
@@ -10545,13 +10566,13 @@
     </row>
     <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
@@ -10579,13 +10600,13 @@
     </row>
     <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
@@ -10613,13 +10634,13 @@
     </row>
     <row r="241" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
@@ -10647,13 +10668,13 @@
     </row>
     <row r="242" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
@@ -10681,13 +10702,13 @@
     </row>
     <row r="243" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
@@ -10715,13 +10736,13 @@
     </row>
     <row r="244" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
@@ -10749,13 +10770,13 @@
     </row>
     <row r="245" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
@@ -10783,13 +10804,13 @@
     </row>
     <row r="246" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
@@ -10817,13 +10838,13 @@
     </row>
     <row r="247" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="3" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
@@ -10851,13 +10872,13 @@
     </row>
     <row r="248" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="3" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
@@ -10885,13 +10906,13 @@
     </row>
     <row r="249" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="3" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
@@ -10919,13 +10940,13 @@
     </row>
     <row r="250" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
@@ -10953,13 +10974,13 @@
     </row>
     <row r="251" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="3" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
@@ -10987,13 +11008,13 @@
     </row>
     <row r="252" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
@@ -11021,13 +11042,13 @@
     </row>
     <row r="253" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
@@ -11055,13 +11076,13 @@
     </row>
     <row r="254" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
@@ -11089,13 +11110,13 @@
     </row>
     <row r="255" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
@@ -11123,13 +11144,13 @@
     </row>
     <row r="256" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
@@ -11157,13 +11178,13 @@
     </row>
     <row r="257" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
@@ -11191,13 +11212,13 @@
     </row>
     <row r="258" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
@@ -11225,13 +11246,13 @@
     </row>
     <row r="259" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
@@ -11259,13 +11280,13 @@
     </row>
     <row r="260" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
@@ -11293,13 +11314,13 @@
     </row>
     <row r="261" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
@@ -11327,13 +11348,13 @@
     </row>
     <row r="262" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
@@ -11361,13 +11382,13 @@
     </row>
     <row r="263" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
@@ -11395,13 +11416,13 @@
     </row>
     <row r="264" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
@@ -11429,13 +11450,13 @@
     </row>
     <row r="265" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="3" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
@@ -11463,13 +11484,13 @@
     </row>
     <row r="266" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
@@ -11497,13 +11518,13 @@
     </row>
     <row r="267" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
@@ -11531,13 +11552,13 @@
     </row>
     <row r="268" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
@@ -11565,13 +11586,13 @@
     </row>
     <row r="269" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
@@ -11599,13 +11620,13 @@
     </row>
     <row r="270" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
@@ -11633,13 +11654,13 @@
     </row>
     <row r="271" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B271" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C271" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
@@ -11667,13 +11688,13 @@
     </row>
     <row r="272" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
@@ -11701,13 +11722,13 @@
     </row>
     <row r="273" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
@@ -11735,13 +11756,13 @@
     </row>
     <row r="274" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
@@ -11769,13 +11790,13 @@
     </row>
     <row r="275" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="1" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
@@ -11803,13 +11824,13 @@
     </row>
     <row r="276" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
@@ -11837,13 +11858,13 @@
     </row>
     <row r="277" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
@@ -11871,13 +11892,13 @@
     </row>
     <row r="278" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="1" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
@@ -11905,13 +11926,13 @@
     </row>
     <row r="279" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="1" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
@@ -11939,13 +11960,13 @@
     </row>
     <row r="280" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
@@ -11973,13 +11994,13 @@
     </row>
     <row r="281" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="1" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
@@ -12007,13 +12028,13 @@
     </row>
     <row r="282" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
@@ -12041,13 +12062,13 @@
     </row>
     <row r="283" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B283" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C283" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
@@ -12075,13 +12096,13 @@
     </row>
     <row r="284" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
@@ -12109,13 +12130,13 @@
     </row>
     <row r="285" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="1" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
@@ -12143,13 +12164,13 @@
     </row>
     <row r="286" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="1" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
@@ -12177,13 +12198,13 @@
     </row>
     <row r="287" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
@@ -12211,13 +12232,13 @@
     </row>
     <row r="288" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288" s="1" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
@@ -12245,13 +12266,13 @@
     </row>
     <row r="289" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289" s="1" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
@@ -12279,13 +12300,13 @@
     </row>
     <row r="290" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290" s="1" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
@@ -12313,13 +12334,13 @@
     </row>
     <row r="291" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="1" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
@@ -12347,13 +12368,13 @@
     </row>
     <row r="292" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="1" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
@@ -12381,13 +12402,13 @@
     </row>
     <row r="293" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="1" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
@@ -12415,13 +12436,13 @@
     </row>
     <row r="294" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="1" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B294" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C294" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
@@ -12449,13 +12470,13 @@
     </row>
     <row r="295" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="1" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
@@ -12483,13 +12504,13 @@
     </row>
     <row r="296" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="1" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
@@ -12517,13 +12538,13 @@
     </row>
     <row r="297" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297" s="1" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
@@ -12551,13 +12572,13 @@
     </row>
     <row r="298" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="1" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
@@ -12585,13 +12606,13 @@
     </row>
     <row r="299" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
@@ -12619,13 +12640,13 @@
     </row>
     <row r="300" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="1" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
@@ -12653,13 +12674,13 @@
     </row>
     <row r="301" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301" s="1" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
@@ -12687,13 +12708,13 @@
     </row>
     <row r="302" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
@@ -12721,13 +12742,13 @@
     </row>
     <row r="303" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
@@ -12755,13 +12776,13 @@
     </row>
     <row r="304" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
@@ -12789,13 +12810,13 @@
     </row>
     <row r="305" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B305" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C305" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
@@ -12823,13 +12844,13 @@
     </row>
     <row r="306" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
@@ -12857,13 +12878,13 @@
     </row>
     <row r="307" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
@@ -12891,13 +12912,13 @@
     </row>
     <row r="308" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="1" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
@@ -12925,13 +12946,13 @@
     </row>
     <row r="309" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
@@ -12959,13 +12980,13 @@
     </row>
     <row r="310" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
@@ -12993,13 +13014,13 @@
     </row>
     <row r="311" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="1" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
@@ -13027,13 +13048,13 @@
     </row>
     <row r="312" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
@@ -13061,13 +13082,13 @@
     </row>
     <row r="313" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
@@ -13095,13 +13116,13 @@
     </row>
     <row r="314" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="1" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
@@ -13129,13 +13150,13 @@
     </row>
     <row r="315" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
@@ -13163,13 +13184,13 @@
     </row>
     <row r="316" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="1" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B316" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C316" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
@@ -13197,13 +13218,13 @@
     </row>
     <row r="317" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="1" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
@@ -13231,13 +13252,13 @@
     </row>
     <row r="318" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="3" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
@@ -13265,13 +13286,13 @@
     </row>
     <row r="319" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="3" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
@@ -13299,13 +13320,13 @@
     </row>
     <row r="320" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="3" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
@@ -13333,13 +13354,13 @@
     </row>
     <row r="321" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="3" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
@@ -13367,13 +13388,13 @@
     </row>
     <row r="322" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322" s="3" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
@@ -13401,13 +13422,13 @@
     </row>
     <row r="323" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323" s="3" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
@@ -13435,13 +13456,13 @@
     </row>
     <row r="324" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="3" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
@@ -13469,13 +13490,13 @@
     </row>
     <row r="325" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="3" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
@@ -13503,13 +13524,13 @@
     </row>
     <row r="326" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="3" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
@@ -13537,13 +13558,13 @@
     </row>
     <row r="327" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="3" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
@@ -13571,13 +13592,13 @@
     </row>
     <row r="328" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="3" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
@@ -13605,13 +13626,13 @@
     </row>
     <row r="329" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="3" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
@@ -13639,13 +13660,13 @@
     </row>
     <row r="330" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="3" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
@@ -13673,13 +13694,13 @@
     </row>
     <row r="331" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="3" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
@@ -13707,13 +13728,13 @@
     </row>
     <row r="332" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="3" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
@@ -13741,13 +13762,13 @@
     </row>
     <row r="333" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A333" s="3" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
@@ -13775,13 +13796,13 @@
     </row>
     <row r="334" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="3" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
@@ -13809,13 +13830,13 @@
     </row>
     <row r="335" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="3" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
@@ -13843,13 +13864,13 @@
     </row>
     <row r="336" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="3" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
@@ -13877,13 +13898,13 @@
     </row>
     <row r="337" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="3" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
@@ -13911,13 +13932,13 @@
     </row>
     <row r="338" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="3" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
@@ -13945,13 +13966,13 @@
     </row>
     <row r="339" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="3" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
@@ -13979,13 +14000,13 @@
     </row>
     <row r="340" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="3" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
@@ -14013,13 +14034,13 @@
     </row>
     <row r="341" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A341" s="3" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
@@ -14047,13 +14068,13 @@
     </row>
     <row r="342" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="3" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
@@ -14081,13 +14102,13 @@
     </row>
     <row r="343" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="3" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
@@ -14115,13 +14136,13 @@
     </row>
     <row r="344" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="3" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
@@ -14149,13 +14170,13 @@
     </row>
     <row r="345" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="3" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
@@ -14183,13 +14204,13 @@
     </row>
     <row r="346" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="3" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
@@ -14217,13 +14238,13 @@
     </row>
     <row r="347" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="3" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
@@ -14251,13 +14272,13 @@
     </row>
     <row r="348" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="3" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
@@ -14285,13 +14306,13 @@
     </row>
     <row r="349" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="3" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
@@ -14319,13 +14340,13 @@
     </row>
     <row r="350" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="3" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
@@ -14353,13 +14374,13 @@
     </row>
     <row r="351" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="3" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
@@ -14387,13 +14408,13 @@
     </row>
     <row r="352" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="3" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
@@ -14421,13 +14442,13 @@
     </row>
     <row r="353" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353" s="3" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
@@ -14455,13 +14476,13 @@
     </row>
     <row r="354" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="3" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
@@ -14489,13 +14510,13 @@
     </row>
     <row r="355" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="3" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
@@ -14523,13 +14544,13 @@
     </row>
     <row r="356" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="3" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
@@ -14557,13 +14578,13 @@
     </row>
     <row r="357" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="3" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
@@ -14591,13 +14612,13 @@
     </row>
     <row r="358" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="3" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
@@ -14625,13 +14646,13 @@
     </row>
     <row r="359" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="3" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
@@ -14659,13 +14680,13 @@
     </row>
     <row r="360" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="3" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
@@ -14693,13 +14714,13 @@
     </row>
     <row r="361" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="3" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
@@ -14727,13 +14748,13 @@
     </row>
     <row r="362" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="3" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
@@ -14761,13 +14782,13 @@
     </row>
     <row r="363" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="3" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
@@ -14795,13 +14816,13 @@
     </row>
     <row r="364" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="3" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D364" s="1"/>
       <c r="E364" s="1"/>
@@ -14829,13 +14850,13 @@
     </row>
     <row r="365" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="3" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D365" s="1"/>
       <c r="E365" s="1"/>
@@ -14863,13 +14884,13 @@
     </row>
     <row r="366" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A366" s="3" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D366" s="1"/>
       <c r="E366" s="1"/>
@@ -14897,13 +14918,13 @@
     </row>
     <row r="367" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A367" s="3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D367" s="1"/>
       <c r="E367" s="1"/>
@@ -14931,13 +14952,13 @@
     </row>
     <row r="368" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="3" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
@@ -14965,13 +14986,13 @@
     </row>
     <row r="369" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="3" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
@@ -14999,13 +15020,13 @@
     </row>
     <row r="370" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="3" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D370" s="1"/>
       <c r="E370" s="1"/>
@@ -15033,13 +15054,13 @@
     </row>
     <row r="371" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D371" s="1"/>
       <c r="E371" s="1"/>
@@ -15067,13 +15088,13 @@
     </row>
     <row r="372" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A372" s="3" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
@@ -15101,13 +15122,13 @@
     </row>
     <row r="373" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="3" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D373" s="1"/>
       <c r="E373" s="1"/>
@@ -15135,13 +15156,13 @@
     </row>
     <row r="374" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="3" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
@@ -15169,13 +15190,13 @@
     </row>
     <row r="375" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="3" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
@@ -15203,13 +15224,13 @@
     </row>
     <row r="376" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="3" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
@@ -15237,13 +15258,13 @@
     </row>
     <row r="377" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="3" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
@@ -15271,13 +15292,13 @@
     </row>
     <row r="378" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="3" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
@@ -15305,13 +15326,13 @@
     </row>
     <row r="379" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="3" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
@@ -15339,13 +15360,13 @@
     </row>
     <row r="380" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="3" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
@@ -15373,13 +15394,13 @@
     </row>
     <row r="381" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="3" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D381" s="1"/>
       <c r="E381" s="1"/>
@@ -15407,13 +15428,13 @@
     </row>
     <row r="382" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="3" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
@@ -15441,13 +15462,13 @@
     </row>
     <row r="383" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="3" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
@@ -15475,13 +15496,13 @@
     </row>
     <row r="384" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="3" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
@@ -15509,13 +15530,13 @@
     </row>
     <row r="385" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="3" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
@@ -15543,13 +15564,13 @@
     </row>
     <row r="386" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="3" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
@@ -15577,13 +15598,13 @@
     </row>
     <row r="387" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="3" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
@@ -15611,13 +15632,13 @@
     </row>
     <row r="388" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="3" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
@@ -15645,13 +15666,13 @@
     </row>
     <row r="389" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="3" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D389" s="1"/>
       <c r="E389" s="1"/>
@@ -15679,13 +15700,13 @@
     </row>
     <row r="390" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="3" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D390" s="1"/>
       <c r="E390" s="1"/>
@@ -15713,13 +15734,13 @@
     </row>
     <row r="391" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="3" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D391" s="1"/>
       <c r="E391" s="1"/>
@@ -15747,13 +15768,13 @@
     </row>
     <row r="392" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="3" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D392" s="1"/>
       <c r="E392" s="1"/>
@@ -15781,13 +15802,13 @@
     </row>
     <row r="393" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="3" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D393" s="1"/>
       <c r="E393" s="1"/>
@@ -15815,13 +15836,13 @@
     </row>
     <row r="394" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="3" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D394" s="1"/>
       <c r="E394" s="1"/>
@@ -15849,13 +15870,13 @@
     </row>
     <row r="395" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="3" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D395" s="1"/>
       <c r="E395" s="1"/>
@@ -15883,13 +15904,13 @@
     </row>
     <row r="396" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="3" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D396" s="1"/>
       <c r="E396" s="1"/>
@@ -15917,13 +15938,13 @@
     </row>
     <row r="397" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="3" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D397" s="1"/>
       <c r="E397" s="1"/>
@@ -15951,13 +15972,13 @@
     </row>
     <row r="398" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="3" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D398" s="1"/>
       <c r="E398" s="1"/>
@@ -15985,13 +16006,13 @@
     </row>
     <row r="399" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="3" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D399" s="1"/>
       <c r="E399" s="1"/>
@@ -16019,13 +16040,13 @@
     </row>
     <row r="400" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="3" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
@@ -16053,13 +16074,13 @@
     </row>
     <row r="401" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="3" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
@@ -16087,13 +16108,13 @@
     </row>
     <row r="402" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="3" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D402" s="1"/>
       <c r="E402" s="1"/>
@@ -16121,13 +16142,13 @@
     </row>
     <row r="403" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="3" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D403" s="1"/>
       <c r="E403" s="1"/>
@@ -16155,13 +16176,13 @@
     </row>
     <row r="404" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="3" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D404" s="1"/>
       <c r="E404" s="1"/>
@@ -16189,13 +16210,13 @@
     </row>
     <row r="405" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="3" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D405" s="1"/>
       <c r="E405" s="1"/>
@@ -16223,13 +16244,13 @@
     </row>
     <row r="406" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="3" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D406" s="1"/>
       <c r="E406" s="1"/>
@@ -16257,13 +16278,13 @@
     </row>
     <row r="407" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="3" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D407" s="1"/>
       <c r="E407" s="1"/>
@@ -16291,13 +16312,13 @@
     </row>
     <row r="408" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="3" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D408" s="1"/>
       <c r="E408" s="1"/>
@@ -16325,13 +16346,13 @@
     </row>
     <row r="409" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="3" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D409" s="1"/>
       <c r="E409" s="1"/>
@@ -16359,13 +16380,13 @@
     </row>
     <row r="410" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="3" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D410" s="1"/>
       <c r="E410" s="1"/>
@@ -16393,13 +16414,13 @@
     </row>
     <row r="411" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="3" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D411" s="1"/>
       <c r="E411" s="1"/>
@@ -16427,13 +16448,13 @@
     </row>
     <row r="412" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="3" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D412" s="1"/>
       <c r="E412" s="1"/>
@@ -16461,13 +16482,13 @@
     </row>
     <row r="413" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="3" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D413" s="1"/>
       <c r="E413" s="1"/>
@@ -16495,13 +16516,13 @@
     </row>
     <row r="414" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="3" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D414" s="1"/>
       <c r="E414" s="1"/>
@@ -16529,13 +16550,13 @@
     </row>
     <row r="415" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="3" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D415" s="1"/>
       <c r="E415" s="1"/>
@@ -16563,13 +16584,13 @@
     </row>
     <row r="416" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="3" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D416" s="1"/>
       <c r="E416" s="1"/>
@@ -16597,13 +16618,13 @@
     </row>
     <row r="417" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D417" s="1"/>
       <c r="E417" s="1"/>
@@ -16631,13 +16652,13 @@
     </row>
     <row r="418" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="3" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D418" s="1"/>
       <c r="E418" s="1"/>
@@ -16665,13 +16686,13 @@
     </row>
     <row r="419" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="3" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D419" s="1"/>
       <c r="E419" s="1"/>
@@ -16699,13 +16720,13 @@
     </row>
     <row r="420" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="3" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D420" s="1"/>
       <c r="E420" s="1"/>
@@ -16733,13 +16754,13 @@
     </row>
     <row r="421" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="3" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D421" s="1"/>
       <c r="E421" s="1"/>
@@ -16767,13 +16788,13 @@
     </row>
     <row r="422" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="3" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D422" s="1"/>
       <c r="E422" s="1"/>
@@ -16801,13 +16822,13 @@
     </row>
     <row r="423" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="3" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D423" s="1"/>
       <c r="E423" s="1"/>
@@ -16835,13 +16856,13 @@
     </row>
     <row r="424" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="3" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D424" s="1"/>
       <c r="E424" s="1"/>
@@ -16869,13 +16890,13 @@
     </row>
     <row r="425" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="3" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D425" s="1"/>
       <c r="E425" s="1"/>
@@ -16903,13 +16924,13 @@
     </row>
     <row r="426" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426" s="3" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D426" s="1"/>
       <c r="E426" s="1"/>
@@ -16937,13 +16958,13 @@
     </row>
     <row r="427" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="3" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D427" s="1"/>
       <c r="E427" s="1"/>
@@ -16971,13 +16992,13 @@
     </row>
     <row r="428" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="3" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D428" s="1"/>
       <c r="E428" s="1"/>
@@ -17005,13 +17026,13 @@
     </row>
     <row r="429" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="3" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D429" s="1"/>
       <c r="E429" s="1"/>
@@ -17039,13 +17060,13 @@
     </row>
     <row r="430" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="3" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D430" s="1"/>
       <c r="E430" s="1"/>
@@ -17073,13 +17094,13 @@
     </row>
     <row r="431" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="3" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D431" s="1"/>
       <c r="E431" s="1"/>
@@ -17107,13 +17128,13 @@
     </row>
     <row r="432" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="3" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D432" s="1"/>
       <c r="E432" s="1"/>
@@ -17141,13 +17162,13 @@
     </row>
     <row r="433" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="3" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D433" s="1"/>
       <c r="E433" s="1"/>
@@ -17175,13 +17196,13 @@
     </row>
     <row r="434" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="3" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D434" s="1"/>
       <c r="E434" s="1"/>
@@ -17209,13 +17230,13 @@
     </row>
     <row r="435" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="3" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D435" s="1"/>
       <c r="E435" s="1"/>
@@ -17243,10 +17264,10 @@
     </row>
     <row r="436" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C436" s="1"/>
       <c r="D436" s="1"/>
@@ -17275,10 +17296,10 @@
     </row>
     <row r="437" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="1" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C437" s="1"/>
       <c r="D437" s="1"/>
@@ -17307,10 +17328,10 @@
     </row>
     <row r="438" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C438" s="1"/>
       <c r="D438" s="1"/>
@@ -17339,10 +17360,10 @@
     </row>
     <row r="439" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="3" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C439" s="1"/>
       <c r="D439" s="1"/>
@@ -17371,10 +17392,10 @@
     </row>
     <row r="440" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="3" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C440" s="1"/>
       <c r="D440" s="1"/>
@@ -17403,10 +17424,10 @@
     </row>
     <row r="441" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="3" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C441" s="1"/>
       <c r="D441" s="1"/>
@@ -17435,10 +17456,10 @@
     </row>
     <row r="442" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="3" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C442" s="1"/>
       <c r="D442" s="1"/>
@@ -17467,10 +17488,10 @@
     </row>
     <row r="443" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="3" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C443" s="1"/>
       <c r="D443" s="1"/>
@@ -17499,10 +17520,10 @@
     </row>
     <row r="444" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A444" s="3" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C444" s="1"/>
       <c r="D444" s="1"/>
@@ -17531,10 +17552,10 @@
     </row>
     <row r="445" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A445" s="3" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="C445" s="1"/>
       <c r="D445" s="1"/>
@@ -17563,10 +17584,10 @@
     </row>
     <row r="446" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A446" s="3" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C446" s="1"/>
       <c r="D446" s="1"/>
@@ -17595,10 +17616,10 @@
     </row>
     <row r="447" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A447" s="3" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C447" s="1"/>
       <c r="D447" s="1"/>
@@ -17627,10 +17648,10 @@
     </row>
     <row r="448" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A448" s="3" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C448" s="1"/>
       <c r="D448" s="1"/>
@@ -17659,10 +17680,10 @@
     </row>
     <row r="449" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A449" s="3" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C449" s="1"/>
       <c r="D449" s="1"/>
@@ -17691,10 +17712,10 @@
     </row>
     <row r="450" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A450" s="3" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C450" s="1"/>
       <c r="D450" s="1"/>
@@ -17723,10 +17744,10 @@
     </row>
     <row r="451" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A451" s="3" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C451" s="1"/>
       <c r="D451" s="1"/>
@@ -17755,10 +17776,10 @@
     </row>
     <row r="452" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C452" s="1"/>
       <c r="D452" s="1"/>
@@ -17787,10 +17808,10 @@
     </row>
     <row r="453" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A453" s="3" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="C453" s="1"/>
       <c r="D453" s="1"/>
@@ -17819,10 +17840,10 @@
     </row>
     <row r="454" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A454" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C454" s="1"/>
       <c r="D454" s="1"/>
@@ -17851,10 +17872,10 @@
     </row>
     <row r="455" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A455" s="3" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C455" s="1"/>
       <c r="D455" s="1"/>
@@ -17883,10 +17904,10 @@
     </row>
     <row r="456" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A456" s="3" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C456" s="1"/>
       <c r="D456" s="1"/>
@@ -17915,10 +17936,10 @@
     </row>
     <row r="457" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A457" s="3" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C457" s="1"/>
       <c r="D457" s="1"/>
@@ -17947,10 +17968,10 @@
     </row>
     <row r="458" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A458" s="3" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C458" s="1"/>
       <c r="D458" s="1"/>
@@ -17979,10 +18000,10 @@
     </row>
     <row r="459" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A459" s="3" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C459" s="1"/>
       <c r="D459" s="1"/>
@@ -18011,10 +18032,10 @@
     </row>
     <row r="460" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A460" s="3" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="C460" s="1"/>
       <c r="D460" s="1"/>
@@ -18043,10 +18064,10 @@
     </row>
     <row r="461" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A461" s="3" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C461" s="1"/>
       <c r="D461" s="1"/>
@@ -18075,10 +18096,10 @@
     </row>
     <row r="462" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A462" s="3" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="C462" s="1"/>
       <c r="D462" s="1"/>
@@ -18107,10 +18128,10 @@
     </row>
     <row r="463" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A463" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="C463" s="1"/>
       <c r="D463" s="1"/>
@@ -18139,10 +18160,10 @@
     </row>
     <row r="464" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A464" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C464" s="1"/>
       <c r="D464" s="1"/>
@@ -18171,10 +18192,10 @@
     </row>
     <row r="465" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="C465" s="1"/>
       <c r="D465" s="1"/>
@@ -18203,10 +18224,10 @@
     </row>
     <row r="466" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="C466" s="1"/>
       <c r="D466" s="1"/>
@@ -18235,10 +18256,10 @@
     </row>
     <row r="467" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="1" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C467" s="1"/>
       <c r="D467" s="1"/>
@@ -18267,10 +18288,10 @@
     </row>
     <row r="468" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="C468" s="1"/>
       <c r="D468" s="1"/>
@@ -18331,10 +18352,10 @@
     </row>
     <row r="470" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="C470" s="1"/>
       <c r="D470" s="1"/>
@@ -18363,10 +18384,10 @@
     </row>
     <row r="471" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="1" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C471" s="1"/>
       <c r="D471" s="1"/>
@@ -18395,10 +18416,10 @@
     </row>
     <row r="472" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="1" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C472" s="1"/>
       <c r="D472" s="1"/>
@@ -18427,10 +18448,10 @@
     </row>
     <row r="473" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="1" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="C473" s="1"/>
       <c r="D473" s="1"/>
@@ -18459,10 +18480,10 @@
     </row>
     <row r="474" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="1" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="C474" s="1"/>
       <c r="D474" s="1"/>
@@ -18491,10 +18512,10 @@
     </row>
     <row r="475" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="1" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="C475" s="1"/>
       <c r="D475" s="1"/>
@@ -33309,50 +33330,50 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -33401,9 +33422,46 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CD247F-14DB-8744-B19A-4D3A306027D6}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1234</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tool/chem.xlsx
+++ b/tool/chem.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pp/Desktop/CS_SWU_68/CP242/organic-chem-app/tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{653D174C-5CC2-B24B-8602-944A277EC37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE5DA53-2BEA-2849-9110-D11CEB6F9584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chemical" sheetId="13" r:id="rId1"/>
     <sheet name="Reaction" sheetId="14" r:id="rId2"/>
     <sheet name="Condition" sheetId="15" r:id="rId3"/>
     <sheet name="User" sheetId="18" r:id="rId4"/>
+    <sheet name="FunctionalGroup" sheetId="19" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="765">
   <si>
     <t>molecularFormula</t>
   </si>
@@ -2195,6 +2196,129 @@
   </si>
   <si>
     <t>name</t>
+  </si>
+  <si>
+    <t>แอลเคน</t>
+  </si>
+  <si>
+    <t>แอลคีน</t>
+  </si>
+  <si>
+    <t>แอลไคน์</t>
+  </si>
+  <si>
+    <t>อะโรมาติก</t>
+  </si>
+  <si>
+    <t>แอลกอฮอล์</t>
+  </si>
+  <si>
+    <t>Ether</t>
+  </si>
+  <si>
+    <t>อีเทอร์</t>
+  </si>
+  <si>
+    <t>Aldehyde</t>
+  </si>
+  <si>
+    <t>แอลดีไฮด์</t>
+  </si>
+  <si>
+    <t>คีโตน</t>
+  </si>
+  <si>
+    <t>Carboxylic acid</t>
+  </si>
+  <si>
+    <t>กรดคาร์บอกซิลิก</t>
+  </si>
+  <si>
+    <t>เอสเทอร์</t>
+  </si>
+  <si>
+    <t>เอมีน</t>
+  </si>
+  <si>
+    <t>เอไมด์</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>groupName</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>พันธะเดี่ยว</t>
+  </si>
+  <si>
+    <t>Alkane.png</t>
+  </si>
+  <si>
+    <t>พันธะคู่</t>
+  </si>
+  <si>
+    <t>Alkene.png</t>
+  </si>
+  <si>
+    <t>พันธะสาม</t>
+  </si>
+  <si>
+    <t>Alkyne.png</t>
+  </si>
+  <si>
+    <t>พันธะเดี่ยวสลับกับพันธะคู่และมีลักษณะเป็นวงกลม</t>
+  </si>
+  <si>
+    <t>Aromatic.png</t>
+  </si>
+  <si>
+    <t>ไฮดรอกซิล</t>
+  </si>
+  <si>
+    <t>Alcohol.png</t>
+  </si>
+  <si>
+    <t>แอลคอกซี</t>
+  </si>
+  <si>
+    <t>Ether.png</t>
+  </si>
+  <si>
+    <t>คาร์บอกซาลดีไฮด์</t>
+  </si>
+  <si>
+    <t>Aldehyde.png</t>
+  </si>
+  <si>
+    <t>คาร์บอนิล</t>
+  </si>
+  <si>
+    <t>Ketone.png</t>
+  </si>
+  <si>
+    <t>คาร์บอกซิล</t>
+  </si>
+  <si>
+    <t>Carboxylic_acid.png</t>
+  </si>
+  <si>
+    <t>แอลคอกซีคาร์บอกนิล</t>
+  </si>
+  <si>
+    <t>Ester.png</t>
+  </si>
+  <si>
+    <t>อะมิโน</t>
+  </si>
+  <si>
+    <t>Amine.png</t>
+  </si>
+  <si>
+    <t>Amide.png</t>
   </si>
 </sst>
 </file>
@@ -33464,4 +33588,202 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853113FE-AFEF-664F-8422-DD030BE2A900}">
+  <dimension ref="A2:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>